--- a/backtest_runs/20260410_193731/by_symbol/ATBA/ATBA.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ATBA/ATBA.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-7409.620000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>92590.38</v>
@@ -771,7 +771,7 @@
         <v>-137.0199999999952</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>98930.19</v>
@@ -909,7 +909,7 @@
         <v>-843.199999999997</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>99072.48</v>
@@ -955,7 +955,7 @@
         <v>-2044.759999999997</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>97027.71999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-1364.930000000002</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>102882.69</v>
@@ -1231,7 +1231,7 @@
         <v>-52.70000000001198</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>102829.99</v>
@@ -1277,7 +1277,7 @@
         <v>-3720.619999999986</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>99109.37</v>
@@ -1323,7 +1323,7 @@
         <v>-690.3700000000013</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>98419</v>
@@ -1461,7 +1461,7 @@
         <v>-1891.930000000002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>100237.15</v>
@@ -1507,7 +1507,7 @@
         <v>-627.1299999999987</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>99610.01999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-3219.969999999992</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>106803.57</v>
